--- a/data/trans_dic/IP44C$hipoteca_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$hipoteca_2023-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de la hipoteca</t>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de la hipoteca (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,4</t>
+          <t>0,0; 3,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,39</t>
+          <t>0,79; 4,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,64</t>
+          <t>0,46; 2,49</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,87</t>
+          <t>0,38; 3,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,42</t>
+          <t>0,64; 3,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,91</t>
+          <t>0,71; 2,85</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,29</t>
+          <t>0,59; 5,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,59</t>
+          <t>0,74; 4,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,7</t>
+          <t>0,96; 3,73</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,02</t>
+          <t>0,57; 1,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,48</t>
+          <t>0,95; 2,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,96</t>
+          <t>0,91; 1,98</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de la hipoteca (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1134</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1134</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4285</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4023</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5037</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5037</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1994; 10868</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2026; 10901</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5635</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>706; 6452</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1153; 6389</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2595; 10455</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3339</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3610</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6949</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>946; 8424</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1314; 8190</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3249; 12624</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11648</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18756</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>3692; 12913</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7086; 18619</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>12766; 27648</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$hipoteca_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$hipoteca_2023-Habitat-trans_dic.xlsx
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,68</t>
+          <t>0,0; 3,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,71</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,33</t>
+          <t>0,82; 4,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,49</t>
+          <t>0,44; 2,46</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,43</t>
+          <t>0,3; 3,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,56</t>
+          <t>0,57; 3,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,85</t>
+          <t>0,69; 2,75</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,23</t>
+          <t>0,55; 5,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,62</t>
+          <t>0,72; 4,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,73</t>
+          <t>0,95; 3,75</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,98</t>
+          <t>0,57; 2,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,5</t>
+          <t>0,89; 2,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,98</t>
+          <t>0,95; 2,0</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4285</t>
+          <t>0; 3727</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4023</t>
+          <t>0; 4321</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1994; 10868</t>
+          <t>2052; 11551</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026; 10901</t>
+          <t>1918; 10783</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>706; 6452</t>
+          <t>571; 6723</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1153; 6389</t>
+          <t>1016; 6175</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2595; 10455</t>
+          <t>2545; 10087</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>946; 8424</t>
+          <t>878; 8241</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1314; 8190</t>
+          <t>1284; 8498</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3249; 12624</t>
+          <t>3207; 12699</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3692; 12913</t>
+          <t>3708; 13012</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7086; 18619</t>
+          <t>6626; 17854</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12766; 27648</t>
+          <t>13303; 27969</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$hipoteca_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$hipoteca_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,75; 4,88</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,82; 4,6</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,46</t>
+          <t>0,51; 2,94</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,58</t>
+          <t>0,58; 3,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,44</t>
+          <t>0,59; 4,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,75</t>
+          <t>0,85; 3,2</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,12</t>
+          <t>0,65; 4,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,79</t>
+          <t>0,59; 5,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,75</t>
+          <t>0,95; 3,83</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,0</t>
+          <t>0,88; 2,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,4</t>
+          <t>0,6; 2,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,0</t>
+          <t>0,93; 2,07</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1125</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3727</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4237</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4321</t>
+          <t>0; 4438</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5131</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5037</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>5131</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1760; 11392</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2052; 11551</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1918; 10783</t>
+          <t>2113; 12201</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>5338</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>571; 6723</t>
+          <t>936; 5383</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1016; 6175</t>
+          <t>913; 7503</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2545; 10087</t>
+          <t>2706; 10133</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>6652</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>878; 8241</t>
+          <t>1076; 7160</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1284; 8498</t>
+          <t>950; 8972</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3207; 12699</t>
+          <t>3091; 12527</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>10917</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18756</t>
+          <t>18245</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3708; 13012</t>
+          <t>6006; 17843</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6626; 17854</t>
+          <t>3722; 13270</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13303; 27969</t>
+          <t>12043; 26960</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$hipoteca_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$hipoteca_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de la hipoteca (tasa de respuesta: 97,81%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,52</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,83</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,75; 4,88</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,51; 2,94</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,58; 3,33</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,59; 4,85</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,85; 3,2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,65; 4,32</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,59; 5,57</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,95; 3,83</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,88; 2,61</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,6; 2,15</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,93; 2,07</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,47 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.009347399194261755</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.004644927098708343</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1125</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1125</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4237</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4438</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>0.03521905393640069</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.01832772435698889</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +603,47 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.02197209184821347</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.01238164194735</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5131</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5131</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.007539155409872349</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="n">
+        <v>0.005099752560508059</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1760; 11392</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2113; 12201</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.0487883780238464</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="n">
+        <v>0.02944371737959066</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +654,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.01625820844833917</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.01749248485191646</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.01686147867237681</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2631</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2707</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5338</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.005785122718835915</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.005899894060126684</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.008548819026936333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>936; 5383</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>913; 7503</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2706; 10133</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.03325941769153486</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.04848868005004191</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.03200937340891186</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +709,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.01901714265831345</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.02172042755893361</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.02034837136654705</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>3155</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>3497</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6652</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.006487536396614347</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.005903809600318392</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.009453836445884708</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>1076; 7160</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>950; 8972</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>3091; 12527</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.04315406238560415</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.05572916251678129</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.03831715580105312</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +764,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.01598245970611355</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.01187869082558752</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.01403503507028383</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>10917</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>7328</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>18245</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.008792060614115627</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.006033139391511819</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.009263849270876739</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>6006; 17843</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>3722; 13270</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>12043; 26960</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.02612090653749811</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.02151036011415169</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.02073837530291405</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +829,441 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de la hipoteca (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1125</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="n">
+        <v>4237</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>4438</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>5131</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1760</v>
+      </c>
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="n">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>11392</v>
+      </c>
+      <c r="D11" s="6" t="inlineStr"/>
+      <c r="E11" s="6" t="n">
+        <v>12201</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>2631</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>2707</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>5338</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>936</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>913</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>5383</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>7503</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>10133</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>3155</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>3497</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>6652</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>1076</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>950</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>3091</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>7160</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>8972</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>12527</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>10917</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>7328</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>18245</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>6006</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>3722</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>12043</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>17843</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>13270</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>26960</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>